--- a/RestaurantManagement.Api/Data/Report.xlsx
+++ b/RestaurantManagement.Api/Data/Report.xlsx
@@ -121,7 +121,70 @@
     <x:t>30</x:t>
   </x:si>
   <x:si>
-    <x:t>31</x:t>
+    <x:t>10897</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Anu preetha kavin</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>p</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> </x:t>
+  </x:si>
+  <x:si>
+    <x:t>h</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>001</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">harish  </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADM001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>John Michael Doe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADM123456</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Johny A. Does</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18UCS5475</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kamali  MohanRaj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mohan  MohanRaj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A2023101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nandhini  s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADM12306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nandhini A. Does</x:t>
   </x:si>
   <x:si>
     <x:t>Number Present Daily</x:t>
@@ -136,13 +199,13 @@
     <x:t>Initials Of Teachers</x:t>
   </x:si>
   <x:si>
-    <x:t>No. on Roll at the beginning of Month: 0  No. of School Days: 0   Average No. on Roll: 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Admitted during the month: 0   Left: 0   Average Attendance: 0   During Month: July</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">No. on Roll at the end of: 0     During Month: July </x:t>
+    <x:t>No. on Roll at the beginning of Month: 8  No. of School Days: 10   Average No. on Roll: 5.38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Admitted during the month: 2   Left: 1   Average Attendance: 4.30   During Month: June</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No. on Roll at the end of: 9     During Month: June </x:t>
   </x:si>
   <x:si>
     <x:t>Certified attendance marked is correct
@@ -808,17 +871,20 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AH10"/>
+  <x:dimension ref="A1:AG19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="4.996339" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.424911" style="0" customWidth="1"/>
-    <x:col min="4" max="12" width="1.710625" style="0" customWidth="1"/>
-    <x:col min="13" max="34" width="2.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.567768" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="6" width="1.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="10" width="1.853482" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="1.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="1.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="33" width="2.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:34" ht="15" customHeight="1">
+    <x:row r="1" spans="1:33" ht="15" customHeight="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -853,10 +919,9 @@
       <x:c r="AD1" s="2"/>
       <x:c r="AE1" s="2"/>
       <x:c r="AF1" s="2"/>
-      <x:c r="AG1" s="2"/>
-      <x:c r="AH1" s="3"/>
+      <x:c r="AG1" s="3"/>
     </x:row>
-    <x:row r="2" spans="1:34" ht="15" customHeight="1">
+    <x:row r="2" spans="1:33" ht="15" customHeight="1">
       <x:c r="A2" s="4" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -891,10 +956,9 @@
       <x:c r="AD2" s="5"/>
       <x:c r="AE2" s="5"/>
       <x:c r="AF2" s="5"/>
-      <x:c r="AG2" s="5"/>
-      <x:c r="AH2" s="6"/>
+      <x:c r="AG2" s="6"/>
     </x:row>
-    <x:row r="3" spans="1:34" ht="14.25" customHeight="1">
+    <x:row r="3" spans="1:33" ht="14.25" customHeight="1">
       <x:c r="A3" s="7" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -991,419 +1055,1314 @@
       <x:c r="AF3" s="8" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="AG3" s="8" t="s">
+      <x:c r="AG3" s="9" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AH3" s="9" t="s">
+    </x:row>
+    <x:row r="4" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A4" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="s">
         <x:v>35</x:v>
       </x:c>
+      <x:c r="C4" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K4" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L4" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M4" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N4" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Q4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="R4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="T4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="W4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="X4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Y4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Z4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AA4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AB4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AC4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AD4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AE4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AF4" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="AG4" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
-    <x:row r="4" spans="1:34" ht="14.25" customHeight="1">
-      <x:c r="A4" s="10" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B4" s="11"/>
-      <x:c r="C4" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="V4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG4" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH4" s="12">
-        <x:v>0</x:v>
+    <x:row r="5" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A5" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L5" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="M5" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N5" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="O5" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P5" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S5" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="U5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="V5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Y5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Z5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AC5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AD5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AE5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AF5" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AG5" s="12" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:34" ht="14.25" customHeight="1">
-      <x:c r="A5" s="10"/>
-      <x:c r="B5" s="11"/>
-      <x:c r="C5" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="U5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="V5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="X5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG5" s="11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH5" s="12">
-        <x:v>0</x:v>
+    <x:row r="6" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A6" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L6" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N6" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O6" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="P6" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S6" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="U6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="V6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Y6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Z6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AC6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AD6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AE6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AF6" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AG6" s="12" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:34" ht="14.25" customHeight="1">
-      <x:c r="A6" s="10" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B6" s="11"/>
-      <x:c r="C6" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D6" s="11"/>
-      <x:c r="E6" s="11"/>
-      <x:c r="F6" s="11"/>
-      <x:c r="G6" s="11"/>
-      <x:c r="H6" s="11"/>
-      <x:c r="I6" s="11"/>
-      <x:c r="J6" s="11"/>
-      <x:c r="K6" s="11"/>
-      <x:c r="L6" s="11"/>
-      <x:c r="M6" s="11"/>
-      <x:c r="N6" s="11"/>
-      <x:c r="O6" s="11"/>
-      <x:c r="P6" s="11"/>
-      <x:c r="Q6" s="11"/>
-      <x:c r="R6" s="11"/>
-      <x:c r="S6" s="11"/>
-      <x:c r="T6" s="11"/>
-      <x:c r="U6" s="11"/>
-      <x:c r="V6" s="11"/>
-      <x:c r="W6" s="11"/>
-      <x:c r="X6" s="11"/>
-      <x:c r="Y6" s="11"/>
-      <x:c r="Z6" s="11"/>
-      <x:c r="AA6" s="11"/>
-      <x:c r="AB6" s="11"/>
-      <x:c r="AC6" s="11"/>
-      <x:c r="AD6" s="11"/>
-      <x:c r="AE6" s="11"/>
-      <x:c r="AF6" s="11"/>
-      <x:c r="AG6" s="11"/>
-      <x:c r="AH6" s="12"/>
+    <x:row r="7" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L7" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N7" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O7" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="P7" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S7" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="T7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="U7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="V7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Y7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Z7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AC7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AD7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AE7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AF7" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AG7" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
-    <x:row r="7" spans="1:34" ht="14.25" customHeight="1">
-      <x:c r="A7" s="10"/>
-      <x:c r="B7" s="11"/>
-      <x:c r="C7" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D7" s="11"/>
-      <x:c r="E7" s="11"/>
-      <x:c r="F7" s="11"/>
-      <x:c r="G7" s="11"/>
-      <x:c r="H7" s="11"/>
-      <x:c r="I7" s="11"/>
-      <x:c r="J7" s="11"/>
-      <x:c r="K7" s="11"/>
-      <x:c r="L7" s="11"/>
-      <x:c r="M7" s="11"/>
-      <x:c r="N7" s="11"/>
-      <x:c r="O7" s="11"/>
-      <x:c r="P7" s="11"/>
-      <x:c r="Q7" s="11"/>
-      <x:c r="R7" s="11"/>
-      <x:c r="S7" s="11"/>
-      <x:c r="T7" s="11"/>
-      <x:c r="U7" s="11"/>
-      <x:c r="V7" s="11"/>
-      <x:c r="W7" s="11"/>
-      <x:c r="X7" s="11"/>
-      <x:c r="Y7" s="11"/>
-      <x:c r="Z7" s="11"/>
-      <x:c r="AA7" s="11"/>
-      <x:c r="AB7" s="11"/>
-      <x:c r="AC7" s="11"/>
-      <x:c r="AD7" s="11"/>
-      <x:c r="AE7" s="11"/>
-      <x:c r="AF7" s="11"/>
-      <x:c r="AG7" s="11"/>
-      <x:c r="AH7" s="12"/>
+    <x:row r="8" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A8" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="O8" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P8" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S8" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="T8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="U8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="V8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Y8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Z8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AC8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AD8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AE8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AF8" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AG8" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
-    <x:row r="8" spans="1:34" ht="15" customHeight="1">
-      <x:c r="A8" s="10" t="s">
+    <x:row r="9" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A9" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L9" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N9" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="O9" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="P9" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="Q9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S9" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="T9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="U9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="V9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Y9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Z9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AC9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AD9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AE9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AF9" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AG9" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A10" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N10" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="O10" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P10" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="Q10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S10" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="T10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="U10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="V10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Y10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Z10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AC10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AD10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AE10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AF10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AG10" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A11" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L11" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N11" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O11" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B8" s="11"/>
-      <x:c r="C8" s="11"/>
-      <x:c r="D8" s="11"/>
-      <x:c r="E8" s="11"/>
-      <x:c r="F8" s="11"/>
-      <x:c r="G8" s="11"/>
-      <x:c r="H8" s="11"/>
-      <x:c r="I8" s="11"/>
-      <x:c r="J8" s="11"/>
-      <x:c r="K8" s="11"/>
-      <x:c r="L8" s="11"/>
-      <x:c r="M8" s="11"/>
-      <x:c r="N8" s="11"/>
-      <x:c r="O8" s="11"/>
-      <x:c r="P8" s="11"/>
-      <x:c r="Q8" s="11"/>
-      <x:c r="R8" s="11"/>
-      <x:c r="S8" s="11"/>
-      <x:c r="T8" s="11"/>
-      <x:c r="U8" s="11"/>
-      <x:c r="V8" s="11"/>
-      <x:c r="W8" s="11"/>
-      <x:c r="X8" s="11"/>
-      <x:c r="Y8" s="11"/>
-      <x:c r="Z8" s="11"/>
-      <x:c r="AA8" s="13" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AB8" s="13"/>
-      <x:c r="AC8" s="13"/>
-      <x:c r="AD8" s="13"/>
-      <x:c r="AE8" s="13"/>
-      <x:c r="AF8" s="13"/>
-      <x:c r="AG8" s="13"/>
-      <x:c r="AH8" s="14"/>
+      <x:c r="P11" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S11" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="U11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="V11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Y11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Z11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AC11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AD11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AE11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AF11" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AG11" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:34" ht="15" customHeight="1">
-      <x:c r="A9" s="10" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B9" s="11"/>
-      <x:c r="C9" s="11"/>
-      <x:c r="D9" s="11"/>
-      <x:c r="E9" s="11"/>
-      <x:c r="F9" s="11"/>
-      <x:c r="G9" s="11"/>
-      <x:c r="H9" s="11"/>
-      <x:c r="I9" s="11"/>
-      <x:c r="J9" s="11"/>
-      <x:c r="K9" s="11"/>
-      <x:c r="L9" s="11"/>
-      <x:c r="M9" s="11"/>
-      <x:c r="N9" s="11"/>
-      <x:c r="O9" s="11"/>
-      <x:c r="P9" s="11"/>
-      <x:c r="Q9" s="11"/>
-      <x:c r="R9" s="11"/>
-      <x:c r="S9" s="11"/>
-      <x:c r="T9" s="11"/>
-      <x:c r="U9" s="11"/>
-      <x:c r="V9" s="11"/>
-      <x:c r="W9" s="11"/>
-      <x:c r="X9" s="11"/>
-      <x:c r="Y9" s="11"/>
-      <x:c r="Z9" s="11"/>
-      <x:c r="AA9" s="13"/>
-      <x:c r="AB9" s="13"/>
-      <x:c r="AC9" s="13"/>
-      <x:c r="AD9" s="13"/>
-      <x:c r="AE9" s="13"/>
-      <x:c r="AF9" s="13"/>
-      <x:c r="AG9" s="13"/>
-      <x:c r="AH9" s="14"/>
+    <x:row r="12" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A12" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L12" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N12" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O12" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="P12" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="R12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S12" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="U12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="V12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="W12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="X12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Y12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="Z12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AA12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AB12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AC12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AD12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AE12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AF12" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="AG12" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:34" ht="15" customHeight="1">
-      <x:c r="A10" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B10" s="16"/>
-      <x:c r="C10" s="16"/>
-      <x:c r="D10" s="16"/>
-      <x:c r="E10" s="16"/>
-      <x:c r="F10" s="16"/>
-      <x:c r="G10" s="16"/>
-      <x:c r="H10" s="16"/>
-      <x:c r="I10" s="16"/>
-      <x:c r="J10" s="16"/>
-      <x:c r="K10" s="16"/>
-      <x:c r="L10" s="16"/>
-      <x:c r="M10" s="16"/>
-      <x:c r="N10" s="16"/>
-      <x:c r="O10" s="16"/>
-      <x:c r="P10" s="16"/>
-      <x:c r="Q10" s="16"/>
-      <x:c r="R10" s="16"/>
-      <x:c r="S10" s="16"/>
-      <x:c r="T10" s="16"/>
-      <x:c r="U10" s="16"/>
-      <x:c r="V10" s="16"/>
-      <x:c r="W10" s="16"/>
-      <x:c r="X10" s="16"/>
-      <x:c r="Y10" s="16"/>
-      <x:c r="Z10" s="16"/>
-      <x:c r="AA10" s="17"/>
-      <x:c r="AB10" s="17"/>
-      <x:c r="AC10" s="17"/>
-      <x:c r="AD10" s="17"/>
-      <x:c r="AE10" s="17"/>
-      <x:c r="AF10" s="17"/>
-      <x:c r="AG10" s="17"/>
-      <x:c r="AH10" s="18"/>
+    <x:row r="13" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A13" s="10" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B13" s="11"/>
+      <x:c r="C13" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H13" s="11">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I13" s="11">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J13" s="11">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="11">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M13" s="11">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N13" s="11">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O13" s="11">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P13" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="11">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF13" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG13" s="12">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A14" s="10"/>
+      <x:c r="B14" s="11"/>
+      <x:c r="C14" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="11">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="11">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I14" s="11">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J14" s="11">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="11">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M14" s="11">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N14" s="11">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O14" s="11">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P14" s="11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" s="11">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF14" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG14" s="12">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A15" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B15" s="11"/>
+      <x:c r="C15" s="11" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D15" s="11"/>
+      <x:c r="E15" s="11"/>
+      <x:c r="F15" s="11"/>
+      <x:c r="G15" s="11"/>
+      <x:c r="H15" s="11"/>
+      <x:c r="I15" s="11"/>
+      <x:c r="J15" s="11"/>
+      <x:c r="K15" s="11"/>
+      <x:c r="L15" s="11"/>
+      <x:c r="M15" s="11"/>
+      <x:c r="N15" s="11"/>
+      <x:c r="O15" s="11"/>
+      <x:c r="P15" s="11"/>
+      <x:c r="Q15" s="11"/>
+      <x:c r="R15" s="11"/>
+      <x:c r="S15" s="11"/>
+      <x:c r="T15" s="11"/>
+      <x:c r="U15" s="11"/>
+      <x:c r="V15" s="11"/>
+      <x:c r="W15" s="11"/>
+      <x:c r="X15" s="11"/>
+      <x:c r="Y15" s="11"/>
+      <x:c r="Z15" s="11"/>
+      <x:c r="AA15" s="11"/>
+      <x:c r="AB15" s="11"/>
+      <x:c r="AC15" s="11"/>
+      <x:c r="AD15" s="11"/>
+      <x:c r="AE15" s="11"/>
+      <x:c r="AF15" s="11"/>
+      <x:c r="AG15" s="12"/>
+    </x:row>
+    <x:row r="16" spans="1:33" ht="14.25" customHeight="1">
+      <x:c r="A16" s="10"/>
+      <x:c r="B16" s="11"/>
+      <x:c r="C16" s="11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D16" s="11"/>
+      <x:c r="E16" s="11"/>
+      <x:c r="F16" s="11"/>
+      <x:c r="G16" s="11"/>
+      <x:c r="H16" s="11"/>
+      <x:c r="I16" s="11"/>
+      <x:c r="J16" s="11"/>
+      <x:c r="K16" s="11"/>
+      <x:c r="L16" s="11"/>
+      <x:c r="M16" s="11"/>
+      <x:c r="N16" s="11"/>
+      <x:c r="O16" s="11"/>
+      <x:c r="P16" s="11"/>
+      <x:c r="Q16" s="11"/>
+      <x:c r="R16" s="11"/>
+      <x:c r="S16" s="11"/>
+      <x:c r="T16" s="11"/>
+      <x:c r="U16" s="11"/>
+      <x:c r="V16" s="11"/>
+      <x:c r="W16" s="11"/>
+      <x:c r="X16" s="11"/>
+      <x:c r="Y16" s="11"/>
+      <x:c r="Z16" s="11"/>
+      <x:c r="AA16" s="11"/>
+      <x:c r="AB16" s="11"/>
+      <x:c r="AC16" s="11"/>
+      <x:c r="AD16" s="11"/>
+      <x:c r="AE16" s="11"/>
+      <x:c r="AF16" s="11"/>
+      <x:c r="AG16" s="12"/>
+    </x:row>
+    <x:row r="17" spans="1:33" ht="15" customHeight="1">
+      <x:c r="A17" s="10" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B17" s="11"/>
+      <x:c r="C17" s="11"/>
+      <x:c r="D17" s="11"/>
+      <x:c r="E17" s="11"/>
+      <x:c r="F17" s="11"/>
+      <x:c r="G17" s="11"/>
+      <x:c r="H17" s="11"/>
+      <x:c r="I17" s="11"/>
+      <x:c r="J17" s="11"/>
+      <x:c r="K17" s="11"/>
+      <x:c r="L17" s="11"/>
+      <x:c r="M17" s="11"/>
+      <x:c r="N17" s="11"/>
+      <x:c r="O17" s="11"/>
+      <x:c r="P17" s="11"/>
+      <x:c r="Q17" s="11"/>
+      <x:c r="R17" s="11"/>
+      <x:c r="S17" s="11"/>
+      <x:c r="T17" s="11"/>
+      <x:c r="U17" s="11"/>
+      <x:c r="V17" s="11"/>
+      <x:c r="W17" s="11"/>
+      <x:c r="X17" s="11"/>
+      <x:c r="Y17" s="11"/>
+      <x:c r="Z17" s="13" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="AA17" s="13"/>
+      <x:c r="AB17" s="13"/>
+      <x:c r="AC17" s="13"/>
+      <x:c r="AD17" s="13"/>
+      <x:c r="AE17" s="13"/>
+      <x:c r="AF17" s="13"/>
+      <x:c r="AG17" s="14"/>
+    </x:row>
+    <x:row r="18" spans="1:33" ht="15" customHeight="1">
+      <x:c r="A18" s="10" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B18" s="11"/>
+      <x:c r="C18" s="11"/>
+      <x:c r="D18" s="11"/>
+      <x:c r="E18" s="11"/>
+      <x:c r="F18" s="11"/>
+      <x:c r="G18" s="11"/>
+      <x:c r="H18" s="11"/>
+      <x:c r="I18" s="11"/>
+      <x:c r="J18" s="11"/>
+      <x:c r="K18" s="11"/>
+      <x:c r="L18" s="11"/>
+      <x:c r="M18" s="11"/>
+      <x:c r="N18" s="11"/>
+      <x:c r="O18" s="11"/>
+      <x:c r="P18" s="11"/>
+      <x:c r="Q18" s="11"/>
+      <x:c r="R18" s="11"/>
+      <x:c r="S18" s="11"/>
+      <x:c r="T18" s="11"/>
+      <x:c r="U18" s="11"/>
+      <x:c r="V18" s="11"/>
+      <x:c r="W18" s="11"/>
+      <x:c r="X18" s="11"/>
+      <x:c r="Y18" s="11"/>
+      <x:c r="Z18" s="13"/>
+      <x:c r="AA18" s="13"/>
+      <x:c r="AB18" s="13"/>
+      <x:c r="AC18" s="13"/>
+      <x:c r="AD18" s="13"/>
+      <x:c r="AE18" s="13"/>
+      <x:c r="AF18" s="13"/>
+      <x:c r="AG18" s="14"/>
+    </x:row>
+    <x:row r="19" spans="1:33" ht="15" customHeight="1">
+      <x:c r="A19" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B19" s="16"/>
+      <x:c r="C19" s="16"/>
+      <x:c r="D19" s="16"/>
+      <x:c r="E19" s="16"/>
+      <x:c r="F19" s="16"/>
+      <x:c r="G19" s="16"/>
+      <x:c r="H19" s="16"/>
+      <x:c r="I19" s="16"/>
+      <x:c r="J19" s="16"/>
+      <x:c r="K19" s="16"/>
+      <x:c r="L19" s="16"/>
+      <x:c r="M19" s="16"/>
+      <x:c r="N19" s="16"/>
+      <x:c r="O19" s="16"/>
+      <x:c r="P19" s="16"/>
+      <x:c r="Q19" s="16"/>
+      <x:c r="R19" s="16"/>
+      <x:c r="S19" s="16"/>
+      <x:c r="T19" s="16"/>
+      <x:c r="U19" s="16"/>
+      <x:c r="V19" s="16"/>
+      <x:c r="W19" s="16"/>
+      <x:c r="X19" s="16"/>
+      <x:c r="Y19" s="16"/>
+      <x:c r="Z19" s="17"/>
+      <x:c r="AA19" s="17"/>
+      <x:c r="AB19" s="17"/>
+      <x:c r="AC19" s="17"/>
+      <x:c r="AD19" s="17"/>
+      <x:c r="AE19" s="17"/>
+      <x:c r="AF19" s="17"/>
+      <x:c r="AG19" s="18"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="8">
-    <x:mergeCell ref="A1:AH1"/>
-    <x:mergeCell ref="A2:AH2"/>
-    <x:mergeCell ref="A4:B5"/>
-    <x:mergeCell ref="A6:B7"/>
-    <x:mergeCell ref="A8:Z8"/>
-    <x:mergeCell ref="AA8:AH10"/>
-    <x:mergeCell ref="A9:Z9"/>
-    <x:mergeCell ref="A10:Z10"/>
+    <x:mergeCell ref="A1:AG1"/>
+    <x:mergeCell ref="A2:AG2"/>
+    <x:mergeCell ref="A13:B14"/>
+    <x:mergeCell ref="A15:B16"/>
+    <x:mergeCell ref="A17:Y17"/>
+    <x:mergeCell ref="Z17:AG19"/>
+    <x:mergeCell ref="A18:Y18"/>
+    <x:mergeCell ref="A19:Y19"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
